--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_2_9.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_2_9.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>222828.7510725867</v>
+        <v>242852.1371432057</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5413711.842050619</v>
+        <v>5117489.517676648</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22726010.95505212</v>
+        <v>22435683.45493321</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3915832.239858635</v>
+        <v>4042435.253264229</v>
       </c>
     </row>
     <row r="11">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2131,13 +2131,13 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="21">
@@ -2198,16 +2198,16 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -2238,22 +2238,22 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.2968606583479628</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2387,19 +2387,19 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>22.56635248423081</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="26">
@@ -2599,16 +2599,16 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2669,13 +2669,13 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
     </row>
     <row r="28">
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2757,16 +2757,16 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>0.2968606583479628</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -2797,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2836,16 +2836,16 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2858,16 +2858,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2982,16 +2982,16 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>22.56635248423082</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3079,13 +3079,13 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="33">
@@ -3107,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3152,16 +3152,16 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -3216,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -3237,13 +3237,13 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>19.8449117491243</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="35">
@@ -3259,10 +3259,10 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -3307,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3386,19 +3386,19 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3420,13 +3420,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>22.56635248423082</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -3468,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -3556,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3626,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>22.56635248423082</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="41">
@@ -3733,13 +3733,13 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>12.57565326968602</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3790,13 +3790,13 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="42">
@@ -3854,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3863,16 +3863,16 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -3939,13 +3939,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
     </row>
     <row r="44">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>24.54405948333093</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>80.44100199269204</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>54.56191997791342</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>50.72300074896607</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>24.84391873418745</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>99.73223474306218</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>99.73223474306218</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>99.73223474306218</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>99.73223474306218</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>99.73223474306218</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>99.73223474306218</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>99.73223474306218</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>50.72300074896607</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>24.84391873418745</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>24.84391873418745</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>76.60208276374469</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>50.72300074896607</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>40.631385380739</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>27.92870531034908</v>
       </c>
     </row>
     <row r="44">
@@ -9381,19 +9381,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L20" t="n">
-        <v>235.7664149699872</v>
+        <v>260.3515428840269</v>
       </c>
       <c r="M20" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N20" t="n">
-        <v>229.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O20" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P20" t="n">
         <v>231.2329957552695</v>
@@ -9463,19 +9463,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
-        <v>138.5543797798742</v>
+        <v>163.1395076939139</v>
       </c>
       <c r="M21" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N21" t="n">
-        <v>131.3417120833333</v>
+        <v>156.9620032779641</v>
       </c>
       <c r="O21" t="n">
-        <v>142.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P21" t="n">
-        <v>133.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q21" t="n">
         <v>139.9817740860215</v>
@@ -9542,16 +9542,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L22" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M22" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N22" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O22" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P22" t="n">
         <v>135.0065633140411</v>
@@ -9618,19 +9618,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L23" t="n">
-        <v>235.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M23" t="n">
-        <v>230.3462332272727</v>
+        <v>254.9313611413124</v>
       </c>
       <c r="N23" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O23" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P23" t="n">
         <v>231.2329957552695</v>
@@ -9697,7 +9697,7 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L24" t="n">
         <v>138.5543797798742</v>
@@ -9706,13 +9706,13 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
-        <v>131.3417120833333</v>
+        <v>155.926839997373</v>
       </c>
       <c r="O24" t="n">
-        <v>142.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P24" t="n">
-        <v>133.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q24" t="n">
         <v>139.9817740860215</v>
@@ -9779,16 +9779,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L25" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M25" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N25" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O25" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P25" t="n">
         <v>135.0065633140411</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L26" t="n">
         <v>235.7664149699872</v>
@@ -9864,13 +9864,13 @@
         <v>230.3462332272727</v>
       </c>
       <c r="N26" t="n">
-        <v>229.4130635965909</v>
+        <v>253.9981915106306</v>
       </c>
       <c r="O26" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P26" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q26" t="n">
         <v>212.3149906599047</v>
@@ -9934,16 +9934,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>137.841438974359</v>
+        <v>162.4265668883987</v>
       </c>
       <c r="L27" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N27" t="n">
-        <v>131.3417120833333</v>
+        <v>156.9620032779641</v>
       </c>
       <c r="O27" t="n">
         <v>142.5962444444444</v>
@@ -10016,16 +10016,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L28" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M28" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N28" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O28" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P28" t="n">
         <v>135.0065633140411</v>
@@ -10092,13 +10092,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L29" t="n">
-        <v>235.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M29" t="n">
-        <v>230.3462332272727</v>
+        <v>254.9313611413124</v>
       </c>
       <c r="N29" t="n">
         <v>229.4130635965909</v>
@@ -10107,7 +10107,7 @@
         <v>230.0982114216867</v>
       </c>
       <c r="P29" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10180,16 +10180,16 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
-        <v>131.3417120833333</v>
+        <v>155.926839997373</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P30" t="n">
-        <v>133.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10253,16 +10253,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L31" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M31" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N31" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O31" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P31" t="n">
         <v>135.0065633140411</v>
@@ -10332,16 +10332,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L32" t="n">
-        <v>235.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M32" t="n">
-        <v>230.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N32" t="n">
-        <v>229.4130635965909</v>
+        <v>253.9981915106306</v>
       </c>
       <c r="O32" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P32" t="n">
         <v>231.2329957552695</v>
@@ -10411,7 +10411,7 @@
         <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>138.5543797798742</v>
+        <v>163.1395076939139</v>
       </c>
       <c r="M33" t="n">
         <v>142.1340339220183</v>
@@ -10420,13 +10420,13 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>142.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P33" t="n">
-        <v>133.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10490,16 +10490,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L34" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M34" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N34" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O34" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P34" t="n">
         <v>135.0065633140411</v>
@@ -10572,16 +10572,16 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M35" t="n">
-        <v>230.3462332272727</v>
+        <v>254.9313611413124</v>
       </c>
       <c r="N35" t="n">
-        <v>229.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O35" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P35" t="n">
-        <v>231.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10645,16 +10645,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M36" t="n">
-        <v>142.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N36" t="n">
-        <v>131.3417120833333</v>
+        <v>155.926839997373</v>
       </c>
       <c r="O36" t="n">
         <v>142.5962444444444</v>
@@ -10727,16 +10727,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L37" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M37" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N37" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O37" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P37" t="n">
         <v>135.0065633140411</v>
@@ -10806,16 +10806,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L38" t="n">
-        <v>235.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M38" t="n">
-        <v>230.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N38" t="n">
-        <v>229.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O38" t="n">
-        <v>230.0982114216867</v>
+        <v>254.6833393357264</v>
       </c>
       <c r="P38" t="n">
         <v>231.2329957552695</v>
@@ -10885,16 +10885,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M39" t="n">
-        <v>142.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N39" t="n">
-        <v>131.3417120833333</v>
+        <v>155.926839997373</v>
       </c>
       <c r="O39" t="n">
-        <v>142.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P39" t="n">
         <v>133.9744074143302</v>
@@ -10964,16 +10964,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L40" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M40" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N40" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O40" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P40" t="n">
         <v>135.0065633140411</v>
@@ -11043,16 +11043,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L41" t="n">
-        <v>235.7664149699872</v>
+        <v>260.3515428840269</v>
       </c>
       <c r="M41" t="n">
-        <v>230.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N41" t="n">
-        <v>229.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O41" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P41" t="n">
         <v>231.2329957552695</v>
@@ -11119,16 +11119,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>137.841438974359</v>
+        <v>162.4265668883987</v>
       </c>
       <c r="L42" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M42" t="n">
-        <v>142.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N42" t="n">
-        <v>131.3417120833333</v>
+        <v>156.9620032779641</v>
       </c>
       <c r="O42" t="n">
         <v>142.5962444444444</v>
@@ -11201,16 +11201,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L43" t="n">
-        <v>134.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M43" t="n">
-        <v>138.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N43" t="n">
-        <v>127.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O43" t="n">
-        <v>138.4565384518428</v>
+        <v>163.0416663658825</v>
       </c>
       <c r="P43" t="n">
         <v>135.0065633140411</v>
@@ -23926,10 +23926,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>382.7338416634806</v>
+        <v>357.1135504688497</v>
       </c>
       <c r="C20" t="n">
-        <v>365.2728917710076</v>
+        <v>342.7065392867767</v>
       </c>
       <c r="D20" t="n">
         <v>354.683041620683</v>
@@ -23989,13 +23989,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>349.240968717413</v>
+        <v>323.6206775227822</v>
       </c>
       <c r="X20" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.2379386560536</v>
+        <v>360.6176474614227</v>
       </c>
     </row>
     <row r="21">
@@ -24056,16 +24056,16 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>171.6831711038378</v>
+        <v>149.116818619607</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>200.321090886344</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>207.1802959547944</v>
       </c>
       <c r="W21" t="n">
         <v>251.6949831609196</v>
@@ -24096,22 +24096,22 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F22" t="n">
-        <v>145.4210480229312</v>
+        <v>145.1241873645833</v>
       </c>
       <c r="G22" t="n">
-        <v>167.9909793584588</v>
+        <v>142.3706881638279</v>
       </c>
       <c r="H22" t="n">
         <v>162.2271725074396</v>
       </c>
       <c r="I22" t="n">
-        <v>155.4504749272583</v>
+        <v>129.8301837326275</v>
       </c>
       <c r="J22" t="n">
-        <v>93.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K22" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -24169,13 +24169,13 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
-        <v>354.683041620683</v>
+        <v>329.0627504260521</v>
       </c>
       <c r="E23" t="n">
-        <v>381.9303700722618</v>
+        <v>356.3100788776309</v>
       </c>
       <c r="F23" t="n">
-        <v>406.8760457417114</v>
+        <v>381.2557545470806</v>
       </c>
       <c r="G23" t="n">
         <v>415.302737515135</v>
@@ -24211,7 +24211,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>149.8691179411497</v>
+        <v>127.3027654569188</v>
       </c>
       <c r="S23" t="n">
         <v>209.0200695862453</v>
@@ -24245,19 +24245,19 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>147.0882077936849</v>
       </c>
       <c r="D24" t="n">
-        <v>147.4450655646388</v>
+        <v>124.8787130804079</v>
       </c>
       <c r="E24" t="n">
-        <v>157.6450804554009</v>
+        <v>132.0247892607701</v>
       </c>
       <c r="F24" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H24" t="n">
         <v>112.2354442364965</v>
@@ -24330,13 +24330,13 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E25" t="n">
-        <v>146.4339626465692</v>
+        <v>123.8676101623384</v>
       </c>
       <c r="F25" t="n">
-        <v>145.4210480229312</v>
+        <v>119.8007568283004</v>
       </c>
       <c r="G25" t="n">
-        <v>167.9909793584588</v>
+        <v>142.3706881638279</v>
       </c>
       <c r="H25" t="n">
         <v>162.2271725074396</v>
@@ -24390,7 +24390,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y25" t="n">
-        <v>218.5846533520948</v>
+        <v>192.964362157464</v>
       </c>
     </row>
     <row r="26">
@@ -24457,16 +24457,16 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>251.3456529078365</v>
+        <v>225.7253617132057</v>
       </c>
       <c r="V26" t="n">
-        <v>327.7522584701349</v>
+        <v>302.1319672755041</v>
       </c>
       <c r="W26" t="n">
-        <v>349.240968717413</v>
+        <v>323.6206775227822</v>
       </c>
       <c r="X26" t="n">
-        <v>369.731100678469</v>
+        <v>347.1647481942382</v>
       </c>
       <c r="Y26" t="n">
         <v>386.2379386560536</v>
@@ -24494,7 +24494,7 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>137.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H27" t="n">
         <v>112.2354442364965</v>
@@ -24527,13 +24527,13 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>100.1578341526431</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S27" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U27" t="n">
         <v>225.9413820809748</v>
@@ -24548,7 +24548,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>205.6826957773044</v>
+        <v>183.1163432930735</v>
       </c>
     </row>
     <row r="28">
@@ -24585,7 +24585,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K28" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -24615,16 +24615,16 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U28" t="n">
-        <v>286.3190293564909</v>
+        <v>286.0221686981429</v>
       </c>
       <c r="V28" t="n">
-        <v>252.137643323828</v>
+        <v>226.5173521291972</v>
       </c>
       <c r="W28" t="n">
-        <v>286.522998336591</v>
+        <v>260.9027071419601</v>
       </c>
       <c r="X28" t="n">
-        <v>225.7096553890372</v>
+        <v>200.0893641944063</v>
       </c>
       <c r="Y28" t="n">
         <v>218.5846533520948</v>
@@ -24655,7 +24655,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H29" t="n">
-        <v>339.4748021157671</v>
+        <v>313.8545109211363</v>
       </c>
       <c r="I29" t="n">
         <v>210.4758895704059</v>
@@ -24694,16 +24694,16 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>251.3456529078365</v>
+        <v>228.7793004236057</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W29" t="n">
-        <v>349.240968717413</v>
+        <v>323.6206775227822</v>
       </c>
       <c r="X29" t="n">
-        <v>369.731100678469</v>
+        <v>344.1108094838382</v>
       </c>
       <c r="Y29" t="n">
         <v>386.2379386560536</v>
@@ -24716,16 +24716,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>144.7134224918944</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>147.0882077936849</v>
       </c>
       <c r="D30" t="n">
-        <v>147.4450655646388</v>
+        <v>121.8247743700079</v>
       </c>
       <c r="E30" t="n">
-        <v>157.6450804554009</v>
+        <v>132.0247892607701</v>
       </c>
       <c r="F30" t="n">
         <v>145.0692123933839</v>
@@ -24740,7 +24740,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24840,16 +24840,16 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q31" t="n">
-        <v>86.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R31" t="n">
-        <v>177.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S31" t="n">
-        <v>224.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T31" t="n">
-        <v>227.9455894282815</v>
+        <v>205.3792369440507</v>
       </c>
       <c r="U31" t="n">
         <v>286.3190293564909</v>
@@ -24889,7 +24889,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>415.302737515135</v>
+        <v>392.7363850309042</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24937,13 +24937,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>349.240968717413</v>
+        <v>323.6206775227822</v>
       </c>
       <c r="X32" t="n">
-        <v>369.731100678469</v>
+        <v>344.1108094838382</v>
       </c>
       <c r="Y32" t="n">
-        <v>386.2379386560536</v>
+        <v>360.6176474614227</v>
       </c>
     </row>
     <row r="33">
@@ -24965,7 +24965,7 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>122.502859909153</v>
       </c>
       <c r="G33" t="n">
         <v>137.3435171632106</v>
@@ -25010,16 +25010,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9413820809748</v>
+        <v>200.321090886344</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>251.6949831609196</v>
+        <v>226.0746919662888</v>
       </c>
       <c r="X33" t="n">
-        <v>205.7729852034775</v>
+        <v>180.1526940088467</v>
       </c>
       <c r="Y33" t="n">
         <v>205.6826957773044</v>
@@ -25032,7 +25032,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>179.8319801819373</v>
+        <v>154.2116889873065</v>
       </c>
       <c r="C34" t="n">
         <v>167.2468210986278</v>
@@ -25074,7 +25074,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>86.16204325169439</v>
@@ -25095,13 +25095,13 @@
         <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
-        <v>286.522998336591</v>
+        <v>266.6780865874667</v>
       </c>
       <c r="X34" t="n">
-        <v>225.7096553890372</v>
+        <v>200.0893641944063</v>
       </c>
       <c r="Y34" t="n">
-        <v>218.5846533520948</v>
+        <v>192.964362157464</v>
       </c>
     </row>
     <row r="35">
@@ -25117,10 +25117,10 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D35" t="n">
-        <v>354.683041620683</v>
+        <v>332.1166891364521</v>
       </c>
       <c r="E35" t="n">
-        <v>381.9303700722618</v>
+        <v>356.3100788776309</v>
       </c>
       <c r="F35" t="n">
         <v>406.8760457417114</v>
@@ -25165,7 +25165,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T35" t="n">
-        <v>223.0958495641314</v>
+        <v>197.4755583695005</v>
       </c>
       <c r="U35" t="n">
         <v>251.3456529078365</v>
@@ -25177,7 +25177,7 @@
         <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
-        <v>369.731100678469</v>
+        <v>344.1108094838382</v>
       </c>
       <c r="Y35" t="n">
         <v>386.2379386560536</v>
@@ -25244,19 +25244,19 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>200.1647286948216</v>
+        <v>174.5444375001908</v>
       </c>
       <c r="U36" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>232.8005871494253</v>
+        <v>210.2342346651944</v>
       </c>
       <c r="W36" t="n">
-        <v>251.6949831609196</v>
+        <v>226.0746919662888</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>180.1526940088467</v>
       </c>
       <c r="Y36" t="n">
         <v>205.6826957773044</v>
@@ -25278,13 +25278,13 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E37" t="n">
-        <v>146.4339626465692</v>
+        <v>120.8136714519383</v>
       </c>
       <c r="F37" t="n">
-        <v>145.4210480229312</v>
+        <v>119.8007568283004</v>
       </c>
       <c r="G37" t="n">
-        <v>167.9909793584588</v>
+        <v>145.424626874228</v>
       </c>
       <c r="H37" t="n">
         <v>162.2271725074396</v>
@@ -25326,7 +25326,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U37" t="n">
-        <v>286.3190293564909</v>
+        <v>260.69873816186</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25348,10 +25348,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>382.7338416634806</v>
+        <v>357.1135504688497</v>
       </c>
       <c r="C38" t="n">
-        <v>365.2728917710076</v>
+        <v>342.7065392867767</v>
       </c>
       <c r="D38" t="n">
         <v>354.683041620683</v>
@@ -25399,7 +25399,7 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>209.0200695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T38" t="n">
         <v>223.0958495641314</v>
@@ -25414,7 +25414,7 @@
         <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
-        <v>369.731100678469</v>
+        <v>344.1108094838382</v>
       </c>
       <c r="Y38" t="n">
         <v>386.2379386560536</v>
@@ -25430,7 +25430,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
-        <v>172.7084989883157</v>
+        <v>147.0882077936849</v>
       </c>
       <c r="D39" t="n">
         <v>147.4450655646388</v>
@@ -25439,7 +25439,7 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F39" t="n">
-        <v>145.0692123933839</v>
+        <v>122.502859909153</v>
       </c>
       <c r="G39" t="n">
         <v>137.3435171632106</v>
@@ -25475,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S39" t="n">
         <v>171.6831711038378</v>
@@ -25484,7 +25484,7 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9413820809748</v>
+        <v>200.321090886344</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25506,10 +25506,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>179.8319801819373</v>
+        <v>154.2116889873065</v>
       </c>
       <c r="C40" t="n">
-        <v>167.2468210986278</v>
+        <v>144.680468614397</v>
       </c>
       <c r="D40" t="n">
         <v>148.6154730182124</v>
@@ -25563,7 +25563,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>286.3190293564909</v>
+        <v>260.69873816186</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25575,7 +25575,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y40" t="n">
-        <v>218.5846533520948</v>
+        <v>192.964362157464</v>
       </c>
     </row>
     <row r="41">
@@ -25591,13 +25591,13 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D41" t="n">
-        <v>354.683041620683</v>
+        <v>329.0627504260521</v>
       </c>
       <c r="E41" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
-        <v>406.8760457417114</v>
+        <v>394.3003924720254</v>
       </c>
       <c r="G41" t="n">
         <v>415.302737515135</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25648,13 +25648,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>349.240968717413</v>
+        <v>323.6206775227822</v>
       </c>
       <c r="X41" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
-        <v>386.2379386560536</v>
+        <v>360.6176474614227</v>
       </c>
     </row>
     <row r="42">
@@ -25712,7 +25712,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>100.1578341526431</v>
+        <v>77.59148166841231</v>
       </c>
       <c r="S42" t="n">
         <v>171.6831711038378</v>
@@ -25721,16 +25721,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>200.321090886344</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>251.6949831609196</v>
+        <v>226.0746919662888</v>
       </c>
       <c r="X42" t="n">
-        <v>205.7729852034775</v>
+        <v>180.1526940088467</v>
       </c>
       <c r="Y42" t="n">
         <v>205.6826957773044</v>
@@ -25743,7 +25743,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>179.8319801819373</v>
+        <v>154.2116889873065</v>
       </c>
       <c r="C43" t="n">
         <v>167.2468210986278</v>
@@ -25797,13 +25797,13 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T43" t="n">
-        <v>227.9455894282815</v>
+        <v>202.3252982336507</v>
       </c>
       <c r="U43" t="n">
         <v>286.3190293564909</v>
       </c>
       <c r="V43" t="n">
-        <v>252.137643323828</v>
+        <v>226.5173521291972</v>
       </c>
       <c r="W43" t="n">
         <v>286.522998336591</v>
@@ -25812,7 +25812,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y43" t="n">
-        <v>218.5846533520948</v>
+        <v>196.018300867864</v>
       </c>
     </row>
     <row r="44">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>338648.3274240562</v>
+        <v>361526.3551190589</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>338648.3274240562</v>
+        <v>361526.3551190589</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>338648.3274240562</v>
+        <v>361526.3551190589</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>338648.3274240562</v>
+        <v>361526.3551190587</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>338648.3274240562</v>
+        <v>361526.3551190589</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>338648.3274240562</v>
+        <v>361526.3551190589</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>338648.3274240562</v>
+        <v>361526.3551190589</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>338648.3274240562</v>
+        <v>361526.3551190588</v>
       </c>
     </row>
     <row r="16">
@@ -26261,7 +26261,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48378.33248915087</v>
+        <v>48378.33248915088</v>
       </c>
       <c r="C2" t="n">
         <v>48378.33248915088</v>
@@ -26273,37 +26273,37 @@
         <v>48378.33248915088</v>
       </c>
       <c r="F2" t="n">
-        <v>48378.33248915088</v>
+        <v>48378.33248915087</v>
       </c>
       <c r="G2" t="n">
         <v>48378.33248915087</v>
       </c>
       <c r="H2" t="n">
+        <v>51644.51686548872</v>
+      </c>
+      <c r="I2" t="n">
+        <v>51644.51686548873</v>
+      </c>
+      <c r="J2" t="n">
+        <v>51644.51686548872</v>
+      </c>
+      <c r="K2" t="n">
+        <v>51644.51686548872</v>
+      </c>
+      <c r="L2" t="n">
+        <v>51644.51686548873</v>
+      </c>
+      <c r="M2" t="n">
+        <v>51644.51686548872</v>
+      </c>
+      <c r="N2" t="n">
+        <v>51644.51686548873</v>
+      </c>
+      <c r="O2" t="n">
+        <v>51644.51686548872</v>
+      </c>
+      <c r="P2" t="n">
         <v>48378.33248915087</v>
-      </c>
-      <c r="I2" t="n">
-        <v>48378.33248915087</v>
-      </c>
-      <c r="J2" t="n">
-        <v>48378.33248915087</v>
-      </c>
-      <c r="K2" t="n">
-        <v>48378.33248915087</v>
-      </c>
-      <c r="L2" t="n">
-        <v>48378.33248915088</v>
-      </c>
-      <c r="M2" t="n">
-        <v>48378.33248915087</v>
-      </c>
-      <c r="N2" t="n">
-        <v>48378.33248915087</v>
-      </c>
-      <c r="O2" t="n">
-        <v>48378.33248915088</v>
-      </c>
-      <c r="P2" t="n">
-        <v>48378.33248915088</v>
       </c>
     </row>
     <row r="3">
@@ -26331,7 +26331,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>6912.585146932151</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10750.74055314464</v>
+        <v>8399.016057144248</v>
       </c>
       <c r="C4" t="n">
-        <v>10750.74055314464</v>
+        <v>8399.016057144248</v>
       </c>
       <c r="D4" t="n">
-        <v>10750.74055314464</v>
+        <v>8399.016057144248</v>
       </c>
       <c r="E4" t="n">
-        <v>10750.74055314464</v>
+        <v>8399.016057144248</v>
       </c>
       <c r="F4" t="n">
-        <v>10750.74055314464</v>
+        <v>8399.016057144248</v>
       </c>
       <c r="G4" t="n">
-        <v>10750.74055314464</v>
+        <v>8399.016057144248</v>
       </c>
       <c r="H4" t="n">
-        <v>10750.74055314464</v>
+        <v>8999.791958765192</v>
       </c>
       <c r="I4" t="n">
-        <v>10750.74055314464</v>
+        <v>8999.791958765192</v>
       </c>
       <c r="J4" t="n">
-        <v>10750.74055314464</v>
+        <v>8999.791958765192</v>
       </c>
       <c r="K4" t="n">
-        <v>10750.74055314464</v>
+        <v>8999.791958765192</v>
       </c>
       <c r="L4" t="n">
-        <v>10750.74055314464</v>
+        <v>8999.791958765192</v>
       </c>
       <c r="M4" t="n">
-        <v>10750.74055314464</v>
+        <v>8999.791958765192</v>
       </c>
       <c r="N4" t="n">
-        <v>10750.74055314464</v>
+        <v>8999.791958765192</v>
       </c>
       <c r="O4" t="n">
-        <v>10750.74055314464</v>
+        <v>8999.791958765192</v>
       </c>
       <c r="P4" t="n">
-        <v>10750.74055314464</v>
+        <v>8399.016057144248</v>
       </c>
     </row>
     <row r="5">
@@ -26435,28 +26435,28 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3999.991936006234</v>
+        <v>6351.716432006637</v>
       </c>
       <c r="C6" t="n">
-        <v>3999.991936006241</v>
+        <v>6351.716432006637</v>
       </c>
       <c r="D6" t="n">
-        <v>3999.991936006241</v>
+        <v>6351.716432006637</v>
       </c>
       <c r="E6" t="n">
-        <v>37627.59193600624</v>
+        <v>39979.31643200664</v>
       </c>
       <c r="F6" t="n">
-        <v>37627.59193600624</v>
+        <v>39979.31643200663</v>
       </c>
       <c r="G6" t="n">
-        <v>37627.59193600623</v>
+        <v>39979.31643200663</v>
       </c>
       <c r="H6" t="n">
-        <v>37627.59193600623</v>
+        <v>34174.42605515783</v>
       </c>
       <c r="I6" t="n">
-        <v>37627.59193600623</v>
+        <v>41087.01120208998</v>
       </c>
       <c r="J6" t="n">
-        <v>37627.59193600623</v>
+        <v>41087.01120208998</v>
       </c>
       <c r="K6" t="n">
-        <v>37627.59193600623</v>
+        <v>41087.01120208998</v>
       </c>
       <c r="L6" t="n">
-        <v>37627.59193600624</v>
+        <v>41087.01120208998</v>
       </c>
       <c r="M6" t="n">
-        <v>37627.59193600623</v>
+        <v>41087.01120208998</v>
       </c>
       <c r="N6" t="n">
-        <v>37627.59193600623</v>
+        <v>41087.01120208998</v>
       </c>
       <c r="O6" t="n">
-        <v>37627.59193600624</v>
+        <v>41087.01120208998</v>
       </c>
       <c r="P6" t="n">
-        <v>37627.59193600624</v>
+        <v>39979.31643200663</v>
       </c>
     </row>
   </sheetData>
@@ -26745,28 +26745,28 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,13 +26892,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26907,34 +26907,34 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,46 +26947,46 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27203,7 +27203,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
   </sheetData>
@@ -36036,19 +36036,19 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -36118,19 +36118,19 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -36197,16 +36197,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>24.58512791403967</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -36273,19 +36273,19 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -36352,7 +36352,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -36361,13 +36361,13 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -36434,16 +36434,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>24.58512791403967</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -36519,13 +36519,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36589,16 +36589,16 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -36671,16 +36671,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>24.58512791403967</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -36747,13 +36747,13 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -36762,7 +36762,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36835,16 +36835,16 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36908,16 +36908,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>24.58512791403967</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -36987,16 +36987,16 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -37066,7 +37066,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -37075,13 +37075,13 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37145,16 +37145,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>24.58512791403967</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -37227,16 +37227,16 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37300,16 +37300,16 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -37382,16 +37382,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>24.58512791403967</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -37461,16 +37461,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37540,16 +37540,16 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -37619,16 +37619,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>24.58512791403967</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -37698,16 +37698,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -37774,16 +37774,16 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -37856,16 +37856,16 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>24.58512791403967</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
